--- a/lab2/пример работы программы с 26 битами.xlsx
+++ b/lab2/пример работы программы с 26 битами.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D0BB1D-10EE-435F-A64F-C1F2EBE8C167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB8BFFD-7EF6-404A-B04E-8F5495F78F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{7AA50DD7-B1F5-4B2E-8E13-5CBBE7739326}"/>
   </bookViews>
@@ -513,82 +513,82 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
       </c>
       <c r="I2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="1">
         <v>1</v>
       </c>
       <c r="K2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1">
         <v>1</v>
       </c>
       <c r="M2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="1">
         <v>1</v>
       </c>
       <c r="O2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="1">
         <v>1</v>
       </c>
       <c r="Q2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="1">
         <v>1</v>
       </c>
       <c r="S2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" s="1">
         <v>1</v>
       </c>
       <c r="U2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" s="1">
         <v>1</v>
       </c>
       <c r="W2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" s="1">
         <v>1</v>
       </c>
       <c r="Y2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" s="1">
         <v>1</v>
       </c>
       <c r="AA2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -596,82 +596,82 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1">
         <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
         <v>1</v>
       </c>
       <c r="L3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="1">
         <v>1</v>
       </c>
       <c r="N3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="1">
         <v>1</v>
       </c>
       <c r="P3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="1">
         <v>1</v>
       </c>
       <c r="R3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="1">
         <v>1</v>
       </c>
       <c r="T3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" s="1">
         <v>1</v>
       </c>
       <c r="V3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" s="1">
         <v>1</v>
       </c>
       <c r="X3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" s="1">
         <v>1</v>
       </c>
       <c r="Z3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="1">
         <v>0</v>
@@ -685,76 +685,76 @@
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
         <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="1">
         <v>1</v>
       </c>
       <c r="K4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="1">
         <v>1</v>
       </c>
       <c r="M4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="1">
         <v>1</v>
       </c>
       <c r="O4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" s="1">
         <v>1</v>
       </c>
       <c r="Q4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="1">
         <v>1</v>
       </c>
       <c r="S4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" s="1">
         <v>1</v>
       </c>
       <c r="U4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" s="1">
         <v>1</v>
       </c>
       <c r="W4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" s="1">
         <v>1</v>
       </c>
       <c r="Y4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="1">
         <v>0</v>
@@ -768,76 +768,76 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
         <v>1</v>
       </c>
       <c r="L5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="1">
         <v>1</v>
       </c>
       <c r="N5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="1">
         <v>1</v>
       </c>
       <c r="P5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="1">
         <v>1</v>
       </c>
       <c r="R5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" s="1">
         <v>1</v>
       </c>
       <c r="T5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="1">
         <v>1</v>
       </c>
       <c r="V5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" s="1">
         <v>1</v>
       </c>
       <c r="X5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="1">
         <v>0</v>
@@ -857,70 +857,70 @@
         <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
       </c>
       <c r="K6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="1">
         <v>1</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="1">
         <v>1</v>
       </c>
       <c r="O6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="1">
         <v>1</v>
       </c>
       <c r="Q6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1">
         <v>1</v>
       </c>
       <c r="S6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" s="1">
         <v>1</v>
       </c>
       <c r="U6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="1">
         <v>1</v>
       </c>
       <c r="W6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
@@ -940,70 +940,70 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
         <v>1</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1">
         <v>1</v>
       </c>
       <c r="J7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
       </c>
       <c r="L7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="1">
         <v>1</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="1">
         <v>1</v>
       </c>
       <c r="P7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="1">
         <v>1</v>
       </c>
       <c r="R7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" s="1">
         <v>1</v>
       </c>
       <c r="T7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="1">
         <v>1</v>
       </c>
       <c r="V7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
@@ -1029,64 +1029,64 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="1">
         <v>1</v>
       </c>
       <c r="K8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="1">
         <v>1</v>
       </c>
       <c r="M8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="1">
         <v>1</v>
       </c>
       <c r="O8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="1">
         <v>1</v>
       </c>
       <c r="Q8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="1">
         <v>1</v>
       </c>
       <c r="S8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="1">
         <v>1</v>
       </c>
       <c r="U8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="AB8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -1112,64 +1112,64 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1">
         <v>1</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
         <v>1</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="1">
         <v>1</v>
       </c>
       <c r="J9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
         <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="1">
         <v>1</v>
       </c>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="1">
         <v>1</v>
       </c>
       <c r="P9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="1">
         <v>1</v>
       </c>
       <c r="R9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" s="1">
         <v>1</v>
       </c>
       <c r="T9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="1">
         <v>0</v>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="AA9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="1">
         <v>0</v>
@@ -1201,58 +1201,58 @@
         <v>1</v>
       </c>
       <c r="C10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="1">
         <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="I10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="1">
         <v>1</v>
       </c>
       <c r="K10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="1">
         <v>1</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="1">
         <v>1</v>
       </c>
       <c r="O10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="1">
         <v>1</v>
       </c>
       <c r="Q10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="1">
         <v>1</v>
       </c>
       <c r="S10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" s="1">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="1">
         <v>0</v>
@@ -1284,58 +1284,58 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="J11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
         <v>1</v>
       </c>
       <c r="L11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="1">
         <v>1</v>
       </c>
       <c r="N11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="1">
         <v>1</v>
       </c>
       <c r="P11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="1">
         <v>1</v>
       </c>
       <c r="R11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" s="1">
         <v>0</v>
@@ -1353,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="Y11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="1">
         <v>0</v>
@@ -1373,52 +1373,52 @@
         <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="1">
         <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
       </c>
       <c r="I12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="1">
         <v>1</v>
       </c>
       <c r="K12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="1">
         <v>1</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="1">
         <v>1</v>
       </c>
       <c r="O12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="1">
         <v>1</v>
       </c>
       <c r="Q12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="1">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         <v>0</v>
       </c>
       <c r="X12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="1">
         <v>0</v>
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="AB12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -1456,52 +1456,52 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1">
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
         <v>1</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="1">
         <v>1</v>
       </c>
       <c r="J13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
         <v>1</v>
       </c>
       <c r="L13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="1">
         <v>1</v>
       </c>
       <c r="N13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="1">
         <v>1</v>
       </c>
       <c r="P13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="1">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="W13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" s="1">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>0</v>
       </c>
       <c r="AA13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -1545,46 +1545,46 @@
         <v>1</v>
       </c>
       <c r="C14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
       </c>
       <c r="E14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1">
         <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="1">
         <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="1">
         <v>1</v>
       </c>
       <c r="M14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="1">
         <v>1</v>
       </c>
       <c r="O14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="1">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" s="1">
         <v>0</v>
@@ -1614,13 +1614,13 @@
         <v>0</v>
       </c>
       <c r="Z14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -1628,46 +1628,46 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
         <v>1</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
         <v>1</v>
       </c>
       <c r="L15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="1">
         <v>1</v>
       </c>
       <c r="N15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="1">
         <v>0</v>
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="U15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="1">
         <v>0</v>
@@ -1697,13 +1697,13 @@
         <v>0</v>
       </c>
       <c r="Y15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="1">
         <v>0</v>
@@ -1717,40 +1717,40 @@
         <v>1</v>
       </c>
       <c r="C16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
       </c>
       <c r="E16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1">
         <v>1</v>
       </c>
       <c r="I16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="1">
         <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="1">
         <v>1</v>
       </c>
       <c r="M16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" s="1">
         <v>0</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="X16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="1">
         <v>0</v>
@@ -1800,40 +1800,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
         <v>1</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" s="1">
         <v>1</v>
       </c>
       <c r="J17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
         <v>1</v>
       </c>
       <c r="L17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="1">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" s="1">
         <v>0</v>
@@ -1863,13 +1863,13 @@
         <v>0</v>
       </c>
       <c r="W17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="1">
         <v>0</v>
@@ -1878,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="AB17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -1889,34 +1889,34 @@
         <v>1</v>
       </c>
       <c r="C18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
       </c>
       <c r="E18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1">
         <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="1">
         <v>1</v>
       </c>
       <c r="I18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="1">
         <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="1">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="R18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" s="1">
         <v>0</v>
@@ -1946,13 +1946,13 @@
         <v>0</v>
       </c>
       <c r="V18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="1">
         <v>0</v>
@@ -1961,10 +1961,10 @@
         <v>1</v>
       </c>
       <c r="AA18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -1972,34 +1972,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
         <v>1</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="1">
         <v>1</v>
       </c>
       <c r="J19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
@@ -2017,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="Q19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" s="1">
         <v>0</v>
@@ -2029,13 +2029,13 @@
         <v>0</v>
       </c>
       <c r="U19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" s="1">
         <v>0</v>
@@ -2044,10 +2044,10 @@
         <v>1</v>
       </c>
       <c r="Z19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" s="1">
         <v>0</v>
@@ -2061,28 +2061,28 @@
         <v>1</v>
       </c>
       <c r="C20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
       </c>
       <c r="E20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
       </c>
       <c r="I20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="1">
         <v>0</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="T20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" s="1">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>1</v>
       </c>
       <c r="Y20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="1">
         <v>0</v>
@@ -2144,28 +2144,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
         <v>1</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="1">
         <v>0</v>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="1">
         <v>0</v>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="S21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="1">
         <v>0</v>
@@ -2210,10 +2210,10 @@
         <v>1</v>
       </c>
       <c r="X21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="1">
         <v>0</v>
@@ -2222,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="AB21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -2233,22 +2233,22 @@
         <v>1</v>
       </c>
       <c r="C22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
       </c>
       <c r="E22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="1">
         <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" s="1">
         <v>0</v>
@@ -2278,13 +2278,13 @@
         <v>0</v>
       </c>
       <c r="R22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" s="1">
         <v>0</v>
@@ -2293,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="W22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="1">
         <v>0</v>
@@ -2305,10 +2305,10 @@
         <v>1</v>
       </c>
       <c r="AA22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -2316,22 +2316,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="1">
         <v>0</v>
@@ -2361,13 +2361,13 @@
         <v>0</v>
       </c>
       <c r="Q23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" s="1">
         <v>0</v>
@@ -2376,10 +2376,10 @@
         <v>1</v>
       </c>
       <c r="V23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23" s="1">
         <v>0</v>
@@ -2388,10 +2388,10 @@
         <v>1</v>
       </c>
       <c r="Z23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="1">
         <v>0</v>
@@ -2405,16 +2405,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="E24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
@@ -2432,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="1">
         <v>0</v>
@@ -2444,13 +2444,13 @@
         <v>0</v>
       </c>
       <c r="P24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" s="1">
         <v>0</v>
@@ -2459,10 +2459,10 @@
         <v>1</v>
       </c>
       <c r="U24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" s="1">
         <v>0</v>
@@ -2471,10 +2471,10 @@
         <v>1</v>
       </c>
       <c r="Y24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="1">
         <v>0</v>
@@ -2488,16 +2488,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C25" s="1">
         <v>1</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -2527,13 +2527,13 @@
         <v>0</v>
       </c>
       <c r="O25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" s="1">
         <v>0</v>
@@ -2542,10 +2542,10 @@
         <v>1</v>
       </c>
       <c r="T25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
@@ -2554,10 +2554,10 @@
         <v>1</v>
       </c>
       <c r="X25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="1">
         <v>0</v>
@@ -2577,10 +2577,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
         <v>0</v>
@@ -2610,13 +2610,13 @@
         <v>0</v>
       </c>
       <c r="N26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="1">
         <v>0</v>
@@ -2625,10 +2625,10 @@
         <v>1</v>
       </c>
       <c r="S26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" s="1">
         <v>0</v>
@@ -2637,10 +2637,10 @@
         <v>1</v>
       </c>
       <c r="W26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="1">
         <v>0</v>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="AB26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -2660,10 +2660,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="1">
         <v>0</v>
@@ -2693,13 +2693,13 @@
         <v>0</v>
       </c>
       <c r="M27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" s="1">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>1</v>
       </c>
       <c r="R27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" s="1">
         <v>0</v>
@@ -2720,10 +2720,10 @@
         <v>1</v>
       </c>
       <c r="V27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X27" s="1">
         <v>0</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AA27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="1">
         <v>0</v>
@@ -2746,7 +2746,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" s="1">
         <v>0</v>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
@@ -2776,13 +2776,13 @@
         <v>0</v>
       </c>
       <c r="L28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" s="1">
         <v>0</v>
@@ -2791,10 +2791,10 @@
         <v>1</v>
       </c>
       <c r="Q28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" s="1">
         <v>0</v>
@@ -2803,10 +2803,10 @@
         <v>1</v>
       </c>
       <c r="U28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" s="1">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0</v>
       </c>
       <c r="Z28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA28" s="1">
         <v>0</v>
       </c>
       <c r="AB28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -2847,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -2859,13 +2859,13 @@
         <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" s="1">
         <v>0</v>
@@ -2874,10 +2874,10 @@
         <v>1</v>
       </c>
       <c r="P29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" s="1">
         <v>0</v>
@@ -2886,10 +2886,10 @@
         <v>1</v>
       </c>
       <c r="T29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="1">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="1">
         <v>0</v>
       </c>
       <c r="AA29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
@@ -2942,13 +2942,13 @@
         <v>0</v>
       </c>
       <c r="J30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="1">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>1</v>
       </c>
       <c r="O30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="1">
         <v>0</v>
@@ -2969,10 +2969,10 @@
         <v>1</v>
       </c>
       <c r="S30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" s="1">
         <v>0</v>
@@ -2984,19 +2984,19 @@
         <v>0</v>
       </c>
       <c r="X30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="1">
         <v>0</v>
       </c>
       <c r="Z30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -3025,13 +3025,13 @@
         <v>0</v>
       </c>
       <c r="I31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
@@ -3040,10 +3040,10 @@
         <v>1</v>
       </c>
       <c r="N31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="1">
         <v>0</v>
@@ -3052,10 +3052,10 @@
         <v>1</v>
       </c>
       <c r="R31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" s="1">
         <v>0</v>
@@ -3067,22 +3067,22 @@
         <v>0</v>
       </c>
       <c r="W31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" s="1">
         <v>0</v>
       </c>
       <c r="Y31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -3123,10 +3123,10 @@
         <v>1</v>
       </c>
       <c r="M32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="1">
         <v>0</v>
@@ -3135,10 +3135,10 @@
         <v>1</v>
       </c>
       <c r="Q32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" s="1">
         <v>0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="V32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32" s="1">
         <v>0</v>
       </c>
       <c r="X32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="C33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
@@ -3191,13 +3191,13 @@
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="1">
         <v>0</v>
@@ -3206,10 +3206,10 @@
         <v>1</v>
       </c>
       <c r="L33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="1">
         <v>0</v>
@@ -3218,10 +3218,10 @@
         <v>1</v>
       </c>
       <c r="P33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" s="1">
         <v>0</v>
@@ -3233,25 +3233,25 @@
         <v>0</v>
       </c>
       <c r="U33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="1">
         <v>0</v>
       </c>
       <c r="W33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" s="1">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C34" s="1">
         <v>0</v>
@@ -3274,13 +3274,13 @@
         <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
@@ -3289,10 +3289,10 @@
         <v>1</v>
       </c>
       <c r="K34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="1">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         <v>1</v>
       </c>
       <c r="O34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="1">
         <v>0</v>
@@ -3316,25 +3316,25 @@
         <v>0</v>
       </c>
       <c r="T34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34" s="1">
         <v>0</v>
       </c>
       <c r="V34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA34" s="1">
         <v>0</v>
@@ -3357,13 +3357,13 @@
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="1">
         <v>0</v>
@@ -3372,10 +3372,10 @@
         <v>1</v>
       </c>
       <c r="J35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -3384,10 +3384,10 @@
         <v>1</v>
       </c>
       <c r="N35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" s="1">
         <v>0</v>
@@ -3399,25 +3399,25 @@
         <v>0</v>
       </c>
       <c r="S35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" s="1">
         <v>0</v>
       </c>
       <c r="U35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="1">
         <v>0</v>
@@ -3440,13 +3440,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
         <v>0</v>
@@ -3455,10 +3455,10 @@
         <v>1</v>
       </c>
       <c r="I36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         <v>1</v>
       </c>
       <c r="M36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" s="1">
         <v>0</v>
@@ -3482,25 +3482,25 @@
         <v>0</v>
       </c>
       <c r="R36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" s="1">
         <v>0</v>
       </c>
       <c r="T36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="1">
         <v>0</v>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="AB36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -3523,13 +3523,13 @@
         <v>0</v>
       </c>
       <c r="C37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -3538,10 +3538,10 @@
         <v>1</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="1">
         <v>0</v>
@@ -3550,10 +3550,10 @@
         <v>1</v>
       </c>
       <c r="L37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="1">
         <v>0</v>
@@ -3565,25 +3565,25 @@
         <v>0</v>
       </c>
       <c r="Q37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" s="1">
         <v>0</v>
       </c>
       <c r="S37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" s="1">
         <v>0</v>
@@ -3595,10 +3595,10 @@
         <v>0</v>
       </c>
       <c r="AA37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -3606,13 +3606,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
         <v>0</v>
@@ -3621,10 +3621,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1">
         <v>0</v>
@@ -3633,10 +3633,10 @@
         <v>1</v>
       </c>
       <c r="K38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="1">
         <v>0</v>
@@ -3648,25 +3648,25 @@
         <v>0</v>
       </c>
       <c r="P38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="1">
         <v>0</v>
       </c>
       <c r="R38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W38" s="1">
         <v>0</v>
@@ -3678,10 +3678,10 @@
         <v>0</v>
       </c>
       <c r="Z38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB38" s="1">
         <v>1</v>
@@ -3692,10 +3692,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
@@ -3704,10 +3704,10 @@
         <v>1</v>
       </c>
       <c r="F39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
         <v>0</v>
@@ -3716,10 +3716,10 @@
         <v>1</v>
       </c>
       <c r="J39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
@@ -3731,25 +3731,25 @@
         <v>0</v>
       </c>
       <c r="O39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" s="1">
         <v>0</v>
       </c>
       <c r="Q39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
@@ -3761,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="Y39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA39" s="1">
         <v>1</v>
@@ -3778,7 +3778,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="1">
         <v>0</v>
@@ -3787,10 +3787,10 @@
         <v>1</v>
       </c>
       <c r="E40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
         <v>0</v>
@@ -3799,10 +3799,10 @@
         <v>1</v>
       </c>
       <c r="I40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
         <v>0</v>
@@ -3814,25 +3814,25 @@
         <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1">
         <v>0</v>
       </c>
       <c r="P40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U40" s="1">
         <v>0</v>
@@ -3844,10 +3844,10 @@
         <v>0</v>
       </c>
       <c r="X40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z40" s="1">
         <v>1</v>
@@ -3856,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="AB40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -3870,10 +3870,10 @@
         <v>1</v>
       </c>
       <c r="D41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -3882,10 +3882,10 @@
         <v>1</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="1">
         <v>0</v>
@@ -3897,25 +3897,25 @@
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="1">
         <v>0</v>
       </c>
       <c r="O41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" s="1">
         <v>0</v>
@@ -3927,10 +3927,10 @@
         <v>0</v>
       </c>
       <c r="W41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y41" s="1">
         <v>1</v>
@@ -3939,10 +3939,10 @@
         <v>0</v>
       </c>
       <c r="AA41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -3953,10 +3953,10 @@
         <v>1</v>
       </c>
       <c r="C42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
@@ -3965,10 +3965,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
@@ -3980,25 +3980,25 @@
         <v>0</v>
       </c>
       <c r="L42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="1">
         <v>0</v>
       </c>
       <c r="N42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" s="1">
         <v>0</v>
@@ -4010,10 +4010,10 @@
         <v>0</v>
       </c>
       <c r="V42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" s="1">
         <v>1</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="Z42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" s="1">
         <v>1</v>
@@ -4036,10 +4036,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
@@ -4048,10 +4048,10 @@
         <v>1</v>
       </c>
       <c r="F43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="1">
         <v>0</v>
@@ -4063,25 +4063,25 @@
         <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="1">
         <v>0</v>
       </c>
       <c r="M43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" s="1">
         <v>0</v>
@@ -4093,10 +4093,10 @@
         <v>0</v>
       </c>
       <c r="U43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="1">
         <v>1</v>
@@ -4105,10 +4105,10 @@
         <v>0</v>
       </c>
       <c r="Y43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA43" s="1">
         <v>1</v>
@@ -4122,7 +4122,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" s="1">
         <v>0</v>
@@ -4131,10 +4131,10 @@
         <v>1</v>
       </c>
       <c r="E44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="1">
         <v>0</v>
@@ -4146,25 +4146,25 @@
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
         <v>0</v>
       </c>
       <c r="L44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="1">
         <v>0</v>
@@ -4176,10 +4176,10 @@
         <v>0</v>
       </c>
       <c r="T44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="1">
         <v>1</v>
@@ -4188,10 +4188,10 @@
         <v>0</v>
       </c>
       <c r="X44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z44" s="1">
         <v>1</v>
@@ -4214,10 +4214,10 @@
         <v>1</v>
       </c>
       <c r="D45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -4229,25 +4229,25 @@
         <v>0</v>
       </c>
       <c r="I45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="1">
         <v>0</v>
       </c>
       <c r="K45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" s="1">
         <v>0</v>
@@ -4259,10 +4259,10 @@
         <v>0</v>
       </c>
       <c r="S45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" s="1">
         <v>1</v>
@@ -4271,10 +4271,10 @@
         <v>0</v>
       </c>
       <c r="W45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" s="1">
         <v>1</v>
@@ -4286,7 +4286,7 @@
         <v>1</v>
       </c>
       <c r="AB45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -4297,10 +4297,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="1">
         <v>0</v>
@@ -4312,25 +4312,25 @@
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
       </c>
       <c r="J46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" s="1">
         <v>0</v>
@@ -4342,10 +4342,10 @@
         <v>0</v>
       </c>
       <c r="R46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="1">
         <v>1</v>
@@ -4354,10 +4354,10 @@
         <v>0</v>
       </c>
       <c r="V46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" s="1">
         <v>1</v>
@@ -4369,10 +4369,10 @@
         <v>1</v>
       </c>
       <c r="AA46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -4380,10 +4380,10 @@
         <v>46</v>
       </c>
       <c r="B47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
@@ -4395,25 +4395,25 @@
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="1">
         <v>0</v>
       </c>
       <c r="I47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" s="1">
         <v>0</v>
@@ -4425,10 +4425,10 @@
         <v>0</v>
       </c>
       <c r="Q47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" s="1">
         <v>1</v>
@@ -4437,10 +4437,10 @@
         <v>0</v>
       </c>
       <c r="U47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="1">
         <v>1</v>
@@ -4452,13 +4452,13 @@
         <v>1</v>
       </c>
       <c r="Z47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -4466,7 +4466,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="1">
         <v>0</v>
@@ -4478,25 +4478,25 @@
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="1">
         <v>0</v>
@@ -4508,10 +4508,10 @@
         <v>0</v>
       </c>
       <c r="P48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="1">
         <v>1</v>
@@ -4520,10 +4520,10 @@
         <v>0</v>
       </c>
       <c r="T48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48" s="1">
         <v>1</v>
@@ -4535,13 +4535,13 @@
         <v>1</v>
       </c>
       <c r="Y48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB48" s="1">
         <v>1</v>
@@ -4561,25 +4561,25 @@
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -4591,10 +4591,10 @@
         <v>0</v>
       </c>
       <c r="O49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="1">
         <v>1</v>
@@ -4603,10 +4603,10 @@
         <v>0</v>
       </c>
       <c r="S49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" s="1">
         <v>1</v>
@@ -4618,13 +4618,13 @@
         <v>1</v>
       </c>
       <c r="X49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA49" s="1">
         <v>1</v>
@@ -4644,25 +4644,25 @@
         <v>0</v>
       </c>
       <c r="D50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
       </c>
       <c r="F50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" s="1">
         <v>0</v>
@@ -4674,10 +4674,10 @@
         <v>0</v>
       </c>
       <c r="N50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="1">
         <v>1</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="R50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" s="1">
         <v>1</v>
@@ -4701,13 +4701,13 @@
         <v>1</v>
       </c>
       <c r="W50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z50" s="1">
         <v>1</v>
@@ -4727,25 +4727,25 @@
         <v>0</v>
       </c>
       <c r="C51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" s="1">
         <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" s="1">
         <v>0</v>
@@ -4757,10 +4757,10 @@
         <v>0</v>
       </c>
       <c r="M51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="1">
         <v>1</v>
@@ -4769,10 +4769,10 @@
         <v>0</v>
       </c>
       <c r="Q51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51" s="1">
         <v>1</v>
@@ -4784,13 +4784,13 @@
         <v>1</v>
       </c>
       <c r="V51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y51" s="1">
         <v>1</v>
@@ -4802,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="AB51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -4810,25 +4810,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="1">
         <v>0</v>
       </c>
       <c r="D52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
@@ -4840,10 +4840,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="1">
         <v>1</v>
@@ -4852,10 +4852,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="1">
         <v>1</v>
@@ -4867,13 +4867,13 @@
         <v>1</v>
       </c>
       <c r="U52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X52" s="1">
         <v>1</v>
@@ -4885,10 +4885,10 @@
         <v>1</v>
       </c>
       <c r="AA52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -4899,19 +4899,19 @@
         <v>0</v>
       </c>
       <c r="C53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" s="1">
         <v>0</v>
@@ -4923,10 +4923,10 @@
         <v>0</v>
       </c>
       <c r="K53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
@@ -4935,10 +4935,10 @@
         <v>0</v>
       </c>
       <c r="O53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" s="1">
         <v>1</v>
@@ -4950,13 +4950,13 @@
         <v>1</v>
       </c>
       <c r="T53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" s="1">
         <v>1</v>
@@ -4968,13 +4968,13 @@
         <v>1</v>
       </c>
       <c r="Z53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -4982,19 +4982,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
@@ -5006,10 +5006,10 @@
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="1">
         <v>1</v>
@@ -5018,10 +5018,10 @@
         <v>0</v>
       </c>
       <c r="N54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" s="1">
         <v>1</v>
@@ -5033,13 +5033,13 @@
         <v>1</v>
       </c>
       <c r="S54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V54" s="1">
         <v>1</v>
@@ -5051,13 +5051,13 @@
         <v>1</v>
       </c>
       <c r="Y54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB54" s="1">
         <v>1</v>
@@ -5068,16 +5068,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -5089,10 +5089,10 @@
         <v>0</v>
       </c>
       <c r="I55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" s="1">
         <v>1</v>
@@ -5101,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="M55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="1">
         <v>1</v>
@@ -5116,13 +5116,13 @@
         <v>1</v>
       </c>
       <c r="R55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U55" s="1">
         <v>1</v>
@@ -5134,13 +5134,13 @@
         <v>1</v>
       </c>
       <c r="X55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA55" s="1">
         <v>1</v>
@@ -5154,13 +5154,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
@@ -5172,10 +5172,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="1">
         <v>1</v>
@@ -5184,10 +5184,10 @@
         <v>0</v>
       </c>
       <c r="L56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" s="1">
         <v>1</v>
@@ -5199,13 +5199,13 @@
         <v>1</v>
       </c>
       <c r="Q56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="1">
         <v>1</v>
@@ -5217,13 +5217,13 @@
         <v>1</v>
       </c>
       <c r="W56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z56" s="1">
         <v>1</v>
@@ -5240,10 +5240,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
@@ -5255,10 +5255,10 @@
         <v>0</v>
       </c>
       <c r="G57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="1">
         <v>1</v>
@@ -5267,10 +5267,10 @@
         <v>0</v>
       </c>
       <c r="K57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
@@ -5282,13 +5282,13 @@
         <v>1</v>
       </c>
       <c r="P57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57" s="1">
         <v>1</v>
@@ -5300,13 +5300,13 @@
         <v>1</v>
       </c>
       <c r="V57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y57" s="1">
         <v>1</v>
@@ -5318,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="AB57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -5326,7 +5326,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" s="1">
         <v>0</v>
@@ -5338,10 +5338,10 @@
         <v>0</v>
       </c>
       <c r="F58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="1">
         <v>1</v>
@@ -5350,10 +5350,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="1">
         <v>1</v>
@@ -5365,13 +5365,13 @@
         <v>1</v>
       </c>
       <c r="O58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" s="1">
         <v>1</v>
@@ -5383,13 +5383,13 @@
         <v>1</v>
       </c>
       <c r="U58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X58" s="1">
         <v>1</v>
@@ -5401,10 +5401,10 @@
         <v>1</v>
       </c>
       <c r="AA58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -5421,10 +5421,10 @@
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -5433,10 +5433,10 @@
         <v>0</v>
       </c>
       <c r="I59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" s="1">
         <v>1</v>
@@ -5448,13 +5448,13 @@
         <v>1</v>
       </c>
       <c r="N59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="1">
         <v>1</v>
@@ -5466,13 +5466,13 @@
         <v>1</v>
       </c>
       <c r="T59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="1">
         <v>1</v>
@@ -5484,13 +5484,13 @@
         <v>1</v>
       </c>
       <c r="Z59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:28" ht="16.5" x14ac:dyDescent="0.25">
@@ -5504,10 +5504,10 @@
         <v>0</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="1">
         <v>1</v>
@@ -5516,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="1">
         <v>1</v>
@@ -5531,13 +5531,13 @@
         <v>1</v>
       </c>
       <c r="M60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P60" s="1">
         <v>1</v>
@@ -5549,13 +5549,13 @@
         <v>1</v>
       </c>
       <c r="S60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" s="1">
         <v>1</v>
@@ -5567,13 +5567,13 @@
         <v>1</v>
       </c>
       <c r="Y60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB60" s="1">
         <v>1</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -5599,10 +5599,10 @@
         <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" s="1">
         <v>1</v>
@@ -5614,13 +5614,13 @@
         <v>1</v>
       </c>
       <c r="L61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" s="1">
         <v>1</v>
@@ -5632,13 +5632,13 @@
         <v>1</v>
       </c>
       <c r="R61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U61" s="1">
         <v>1</v>
@@ -5650,13 +5650,13 @@
         <v>1</v>
       </c>
       <c r="X61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA61" s="1">
         <v>1</v>
